--- a/ibge_dados/df_final.xlsx
+++ b/ibge_dados/df_final.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Convencional</t>
+          <t>Tratamento_Convencional</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Nao_Convencional</t>
+          <t>Tratamento_Nao_Convencional</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
